--- a/2026 IMI Golf League.xlsx
+++ b/2026 IMI Golf League.xlsx
@@ -9842,21 +9842,25 @@
       <c r="G15" s="220" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="220" t="n"/>
-      <c r="I15" s="220" t="n"/>
+      <c r="H15" s="220" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="220" t="n">
+        <v>1</v>
+      </c>
       <c r="J15" s="220" t="n"/>
       <c r="K15" s="220" t="n"/>
       <c r="L15" s="160" t="n"/>
       <c r="M15" s="222" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N15" s="220" t="inlineStr">
         <is>
-          <t>1-3-0</t>
+          <t>1-5-0</t>
         </is>
       </c>
       <c r="O15" s="230" t="n">
-        <v>46.2</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="16" ht="13.5" customHeight="1" s="197" thickBot="1">
@@ -9878,8 +9882,12 @@
       <c r="G16" s="163" t="n">
         <v>49</v>
       </c>
-      <c r="H16" s="163" t="n"/>
-      <c r="I16" s="163" t="n"/>
+      <c r="H16" s="163" t="n">
+        <v>48</v>
+      </c>
+      <c r="I16" s="163" t="n">
+        <v>48</v>
+      </c>
       <c r="J16" s="163" t="n"/>
       <c r="K16" s="163" t="n"/>
       <c r="L16" s="164" t="n"/>
@@ -9918,17 +9926,19 @@
       <c r="K17" s="166" t="n">
         <v>1</v>
       </c>
-      <c r="L17" s="167" t="n"/>
+      <c r="L17" s="167" t="n">
+        <v>7</v>
+      </c>
       <c r="M17" s="226" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="N17" s="218" t="inlineStr">
         <is>
-          <t>4-1-0</t>
+          <t>5-1-0</t>
         </is>
       </c>
       <c r="O17" s="212" t="n">
-        <v>37.4</v>
+        <v>36.7</v>
       </c>
       <c r="Q17" s="227" t="inlineStr">
         <is>
@@ -9961,7 +9971,9 @@
       <c r="K18" s="170" t="n">
         <v>40</v>
       </c>
-      <c r="L18" s="171" t="n"/>
+      <c r="L18" s="171" t="n">
+        <v>33</v>
+      </c>
       <c r="M18" s="223" t="n"/>
       <c r="N18" s="219" t="n"/>
       <c r="O18" s="213" t="n"/>
@@ -10081,22 +10093,24 @@
         <v>8</v>
       </c>
       <c r="H21" s="166" t="n"/>
-      <c r="I21" s="166" t="n"/>
+      <c r="I21" s="166" t="n">
+        <v>7</v>
+      </c>
       <c r="J21" s="166" t="n"/>
       <c r="K21" s="166" t="n">
         <v>6</v>
       </c>
       <c r="L21" s="167" t="n"/>
       <c r="M21" s="226" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="N21" s="218" t="inlineStr">
         <is>
-          <t>4-0-0</t>
+          <t>5-0-0</t>
         </is>
       </c>
       <c r="O21" s="212" t="n">
-        <v>39.2</v>
+        <v>38.6</v>
       </c>
       <c r="Q21" s="154" t="inlineStr">
         <is>
@@ -10123,7 +10137,9 @@
         <v>41</v>
       </c>
       <c r="H22" s="170" t="n"/>
-      <c r="I22" s="170" t="n"/>
+      <c r="I22" s="170" t="n">
+        <v>36</v>
+      </c>
       <c r="J22" s="170" t="n"/>
       <c r="K22" s="170" t="n">
         <v>39</v>

--- a/2026 IMI Golf League.xlsx
+++ b/2026 IMI Golf League.xlsx
@@ -9930,7 +9930,7 @@
         <v>7</v>
       </c>
       <c r="M17" s="226" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="N17" s="218" t="inlineStr">
         <is>
